--- a/artfynd/A 20948-2026 artfynd.xlsx
+++ b/artfynd/A 20948-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4340728</v>
       </c>
       <c r="B2" t="n">
-        <v>96353</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512425.759085966</v>
+        <v>512426</v>
       </c>
       <c r="R2" t="n">
-        <v>7093696.753507342</v>
+        <v>7093697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>1999-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5891836</v>
+        <v>4865408</v>
       </c>
       <c r="B3" t="n">
-        <v>96245</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,33 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223578</v>
+        <v>222467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renålandet, Jmt</t>
+          <t>Görmyran 1,9 km S Renålandet bägge sidor av vägen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512235.9771692717</v>
+        <v>512363</v>
       </c>
       <c r="R3" t="n">
-        <v>7093299.299576454</v>
+        <v>7093556</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1999-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1947-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1947-08-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Helge Stenar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,20 +873,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -917,12 +896,7 @@
         <v>6454842</v>
       </c>
       <c r="B4" t="n">
-        <v>96244</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512362.536884904</v>
+        <v>512363</v>
       </c>
       <c r="R4" t="n">
-        <v>7093555.92640999</v>
+        <v>7093556</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -987,19 +961,9 @@
           <t>1947-08-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1947-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1036,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4865408</v>
+        <v>5891836</v>
       </c>
       <c r="B5" t="n">
-        <v>97307</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,37 +1011,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222467</v>
+        <v>223578</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Görmyran 1,9 km S Renålandet bägge sidor av vägen, Jmt</t>
+          <t>Renålandet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512362.536884904</v>
+        <v>512236</v>
       </c>
       <c r="R5" t="n">
-        <v>7093555.92640999</v>
+        <v>7093299</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,27 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1947-08-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1947-08-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Helge Stenar</t>
+          <t>1999-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,20 +1078,20 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Rikkärr</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 20948-2026 artfynd.xlsx
+++ b/artfynd/A 20948-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4340728</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4865408</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6454842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,8 +1115,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5891836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>